--- a/output_excel/hosp1_resultados.xlsx
+++ b/output_excel/hosp1_resultados.xlsx
@@ -16,7 +16,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="17">
+  <si>
+    <t>KNN_mean</t>
+  </si>
+  <si>
+    <t>KNN_std</t>
+  </si>
   <si>
     <t>LPMD_mean</t>
   </si>
@@ -24,6 +30,18 @@
     <t>LPMD_std</t>
   </si>
   <si>
+    <t>LPMD2_mean</t>
+  </si>
+  <si>
+    <t>LPMD2_std</t>
+  </si>
+  <si>
+    <t>MICE_mean</t>
+  </si>
+  <si>
+    <t>MICE_std</t>
+  </si>
+  <si>
     <t>Mean_mean</t>
   </si>
   <si>
@@ -34,6 +52,12 @@
   </si>
   <si>
     <t>PMIVAE_std</t>
+  </si>
+  <si>
+    <t>SAEI_mean</t>
+  </si>
+  <si>
+    <t>SAEI_std</t>
   </si>
   <si>
     <t>auc</t>
@@ -400,10 +424,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -422,39 +446,87 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B2">
-        <v>0.6753080367356277</v>
+        <v>0.7130818925602729</v>
       </c>
       <c r="C2">
-        <v>0.06160257822219413</v>
+        <v>0.06494454405185496</v>
       </c>
       <c r="D2">
+        <v>0.7150809992265037</v>
+      </c>
+      <c r="E2">
+        <v>0.04865804266652551</v>
+      </c>
+      <c r="F2">
+        <v>0.7176809273240294</v>
+      </c>
+      <c r="G2">
+        <v>0.05353482388865948</v>
+      </c>
+      <c r="H2">
+        <v>0.7151643407305727</v>
+      </c>
+      <c r="I2">
+        <v>0.06249925647103194</v>
+      </c>
+      <c r="J2">
         <v>0.7180791145101372</v>
       </c>
-      <c r="E2">
+      <c r="K2">
         <v>0.04853627984245161</v>
       </c>
-      <c r="F2">
-        <v>0.5898277064200194</v>
-      </c>
-      <c r="G2">
-        <v>0.147181747980591</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="L2">
+        <v>0.716448235665806</v>
+      </c>
+      <c r="M2">
+        <v>0.04902189175698916</v>
+      </c>
+      <c r="N2">
+        <v>0.7157755117604122</v>
+      </c>
+      <c r="O2">
+        <v>0.03541174498437542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3">
-        <v>0.5428571428571429</v>
+        <v>0.6047619047619047</v>
       </c>
       <c r="C3">
-        <v>0.03912303982179757</v>
+        <v>0.08518354199999199</v>
       </c>
       <c r="D3">
         <v>0.5714285714285714</v>
@@ -463,33 +535,81 @@
         <v>0.08748177652797065</v>
       </c>
       <c r="F3">
-        <v>0.3761904761904762</v>
+        <v>0.6047619047619047</v>
       </c>
       <c r="G3">
-        <v>0.2064712703683695</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>0.08518354199999199</v>
+      </c>
+      <c r="H3">
+        <v>0.6047619047619047</v>
+      </c>
+      <c r="I3">
+        <v>0.08518354199999199</v>
+      </c>
+      <c r="J3">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K3">
+        <v>0.08748177652797065</v>
+      </c>
+      <c r="L3">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="M3">
+        <v>0.08748177652797065</v>
+      </c>
+      <c r="N3">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="O3">
+        <v>0.08748177652797065</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>0.6973919011667811</v>
+        <v>0.6824525280256234</v>
       </c>
       <c r="C4">
-        <v>0.05779391455567295</v>
+        <v>0.03025055747154673</v>
       </c>
       <c r="D4">
+        <v>0.7060398078242965</v>
+      </c>
+      <c r="E4">
+        <v>0.05051730001818518</v>
+      </c>
+      <c r="F4">
+        <v>0.7166781056966369</v>
+      </c>
+      <c r="G4">
+        <v>0.06595126079253961</v>
+      </c>
+      <c r="H4">
+        <v>0.6974376572866622</v>
+      </c>
+      <c r="I4">
+        <v>0.03500100176534015</v>
+      </c>
+      <c r="J4">
         <v>0.6952871196522535</v>
       </c>
-      <c r="E4">
+      <c r="K4">
         <v>0.03602789635377044</v>
       </c>
-      <c r="F4">
-        <v>0.5001143902997025</v>
-      </c>
-      <c r="G4">
-        <v>0.05028257202823844</v>
+      <c r="L4">
+        <v>0.6995881949210707</v>
+      </c>
+      <c r="M4">
+        <v>0.04145685007100892</v>
+      </c>
+      <c r="N4">
+        <v>0.6952642415923129</v>
+      </c>
+      <c r="O4">
+        <v>0.01657909722605517</v>
       </c>
     </row>
   </sheetData>
@@ -499,10 +619,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -521,74 +641,170 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B2">
-        <v>0.6724281247616868</v>
+        <v>0.6952212090509962</v>
       </c>
       <c r="C2">
-        <v>0.1298827780764386</v>
+        <v>0.08105318699970293</v>
       </c>
       <c r="D2">
+        <v>0.7215154535847741</v>
+      </c>
+      <c r="E2">
+        <v>0.1214615059207974</v>
+      </c>
+      <c r="F2">
+        <v>0.6293688923750695</v>
+      </c>
+      <c r="G2">
+        <v>0.03943202183913422</v>
+      </c>
+      <c r="H2">
+        <v>0.6491556906450523</v>
+      </c>
+      <c r="I2">
+        <v>0.1106884314259497</v>
+      </c>
+      <c r="J2">
         <v>0.7065142552102058</v>
       </c>
-      <c r="E2">
+      <c r="K2">
         <v>0.1554420232386667</v>
       </c>
-      <c r="F2">
-        <v>0.5027470013400006</v>
-      </c>
-      <c r="G2">
-        <v>0.1668141971911657</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="L2">
+        <v>0.6568549748886057</v>
+      </c>
+      <c r="M2">
+        <v>0.1081386481015139</v>
+      </c>
+      <c r="N2">
+        <v>0.5626128923314921</v>
+      </c>
+      <c r="O2">
+        <v>0.06927664710377918</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0.6714285714285715</v>
       </c>
       <c r="C3">
-        <v>0.149071198499986</v>
+        <v>0.1994891434824135</v>
       </c>
       <c r="D3">
+        <v>0.7571428571428572</v>
+      </c>
+      <c r="E3">
+        <v>0.1653005234067599</v>
+      </c>
+      <c r="F3">
+        <v>0.6619047619047619</v>
+      </c>
+      <c r="G3">
+        <v>0.1980631842198612</v>
+      </c>
+      <c r="H3">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="I3">
+        <v>0.2706337569215776</v>
+      </c>
+      <c r="J3">
         <v>0.7285714285714285</v>
       </c>
-      <c r="E3">
+      <c r="K3">
         <v>0.2113556287730681</v>
       </c>
-      <c r="F3">
-        <v>0.4047619047619048</v>
-      </c>
-      <c r="G3">
-        <v>0.3794613678692673</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="L3">
+        <v>0.6761904761904762</v>
+      </c>
+      <c r="M3">
+        <v>0.2113556287730681</v>
+      </c>
+      <c r="N3">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="O3">
+        <v>0.2371409447235949</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>0.5598261267444521</v>
+        <v>0.5947151681537405</v>
       </c>
       <c r="C4">
-        <v>0.1027293676066154</v>
+        <v>0.09354098458493909</v>
       </c>
       <c r="D4">
+        <v>0.5728208647906657</v>
+      </c>
+      <c r="E4">
+        <v>0.08949641479841186</v>
+      </c>
+      <c r="F4">
+        <v>0.5257606954930222</v>
+      </c>
+      <c r="G4">
+        <v>0.167118480848116</v>
+      </c>
+      <c r="H4">
+        <v>0.6054221002059026</v>
+      </c>
+      <c r="I4">
+        <v>0.1155974285117565</v>
+      </c>
+      <c r="J4">
         <v>0.5343857240905971</v>
       </c>
-      <c r="E4">
+      <c r="K4">
         <v>0.08782499544937888</v>
       </c>
-      <c r="F4">
-        <v>0.5707389613360787</v>
-      </c>
-      <c r="G4">
-        <v>0.06768337834691536</v>
+      <c r="L4">
+        <v>0.5215511324639671</v>
+      </c>
+      <c r="M4">
+        <v>0.0900967076852254</v>
+      </c>
+      <c r="N4">
+        <v>0.6007778540379776</v>
+      </c>
+      <c r="O4">
+        <v>0.09931252246114686</v>
       </c>
     </row>
   </sheetData>
@@ -598,10 +814,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:15">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -620,74 +836,170 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B2">
-        <v>0.7051895065965073</v>
+        <v>0.706600320292839</v>
       </c>
       <c r="C2">
-        <v>0.0431518104006658</v>
+        <v>0.07243849161300098</v>
       </c>
       <c r="D2">
+        <v>0.7089159067882471</v>
+      </c>
+      <c r="E2">
+        <v>0.05824215213001974</v>
+      </c>
+      <c r="F2">
+        <v>0.7021859441557451</v>
+      </c>
+      <c r="G2">
+        <v>0.07348025488701905</v>
+      </c>
+      <c r="H2">
+        <v>0.7211790916320773</v>
+      </c>
+      <c r="I2">
+        <v>0.05041731822667232</v>
+      </c>
+      <c r="J2">
         <v>0.7348983015764072</v>
       </c>
-      <c r="E2">
+      <c r="K2">
         <v>0.07606687059164607</v>
       </c>
-      <c r="F2">
-        <v>0.4123067621008595</v>
-      </c>
-      <c r="G2">
-        <v>0.112356691406537</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="L2">
+        <v>0.7394025558061248</v>
+      </c>
+      <c r="M2">
+        <v>0.05070249026532829</v>
+      </c>
+      <c r="N2">
+        <v>0.6901962065997755</v>
+      </c>
+      <c r="O2">
+        <v>0.05829207720319476</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3">
-        <v>0.5809523809523809</v>
+        <v>0.7</v>
       </c>
       <c r="C3">
-        <v>0.1730085916627138</v>
+        <v>0.1713624210994913</v>
       </c>
       <c r="D3">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="E3">
+        <v>0.2064712703683695</v>
+      </c>
+      <c r="F3">
+        <v>0.7285714285714286</v>
+      </c>
+      <c r="G3">
+        <v>0.1185704723617975</v>
+      </c>
+      <c r="H3">
         <v>0.7</v>
       </c>
-      <c r="E3">
+      <c r="I3">
+        <v>0.1713624210994913</v>
+      </c>
+      <c r="J3">
+        <v>0.7</v>
+      </c>
+      <c r="K3">
         <v>0.138423255749987</v>
       </c>
-      <c r="F3">
-        <v>0.3619047619047618</v>
-      </c>
-      <c r="G3">
-        <v>0.06388765649999396</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="L3">
+        <v>0.7</v>
+      </c>
+      <c r="M3">
+        <v>0.138423255749987</v>
+      </c>
+      <c r="N3">
+        <v>0.6095238095238095</v>
+      </c>
+      <c r="O3">
+        <v>0.05216405309573011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>0.6588194921070694</v>
+        <v>0.6674445207046442</v>
       </c>
       <c r="C4">
-        <v>0.0786594313919972</v>
+        <v>0.06359886692397383</v>
       </c>
       <c r="D4">
+        <v>0.6995424388011896</v>
+      </c>
+      <c r="E4">
+        <v>0.04887462600348768</v>
+      </c>
+      <c r="F4">
+        <v>0.5280713795470143</v>
+      </c>
+      <c r="G4">
+        <v>0.117223258902481</v>
+      </c>
+      <c r="H4">
+        <v>0.6460077785403797</v>
+      </c>
+      <c r="I4">
+        <v>0.06947247906446173</v>
+      </c>
+      <c r="J4">
         <v>0.6673758865248226</v>
       </c>
-      <c r="E4">
+      <c r="K4">
         <v>0.07093657830260734</v>
       </c>
-      <c r="F4">
-        <v>0.4722489132921528</v>
-      </c>
-      <c r="G4">
-        <v>0.09171069193476336</v>
+      <c r="L4">
+        <v>0.6609700297414779</v>
+      </c>
+      <c r="M4">
+        <v>0.05748305483740741</v>
+      </c>
+      <c r="N4">
+        <v>0.6910318005033173</v>
+      </c>
+      <c r="O4">
+        <v>0.0421403679394308</v>
       </c>
     </row>
   </sheetData>

--- a/output_excel/hosp1_resultados.xlsx
+++ b/output_excel/hosp1_resultados.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flopes\Documents\GitHub\Doutorado-real-datasets\output_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="SVM" sheetId="1" r:id="rId1"/>
-    <sheet name="GB" sheetId="2" r:id="rId2"/>
-    <sheet name="RF" sheetId="3" r:id="rId3"/>
+    <sheet name="(a) Gradient Boosting" sheetId="2" r:id="rId1"/>
+    <sheet name="(b) Random Forest" sheetId="3" r:id="rId2"/>
+    <sheet name="(c) Support Vector Machine" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -72,8 +77,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +141,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Escritório">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -180,9 +193,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Escritório">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -214,9 +227,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -248,9 +262,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Escritório">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,11 +438,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,145 +486,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.7130818925602729</v>
+        <v>0.69522120905099616</v>
       </c>
       <c r="C2">
-        <v>0.06494454405185496</v>
+        <v>8.1053186999702931E-2</v>
       </c>
       <c r="D2">
-        <v>0.7150809992265037</v>
+        <v>0.72151545358477409</v>
       </c>
       <c r="E2">
-        <v>0.04865804266652551</v>
+        <v>0.12146150592079739</v>
       </c>
       <c r="F2">
-        <v>0.7176809273240294</v>
+        <v>0.62936889237506954</v>
       </c>
       <c r="G2">
-        <v>0.05353482388865948</v>
+        <v>3.9432021839134218E-2</v>
       </c>
       <c r="H2">
-        <v>0.7151643407305727</v>
+        <v>0.6491556906450523</v>
       </c>
       <c r="I2">
-        <v>0.06249925647103194</v>
+        <v>0.1106884314259497</v>
       </c>
       <c r="J2">
-        <v>0.7180791145101372</v>
+        <v>0.70651425521020583</v>
       </c>
       <c r="K2">
-        <v>0.04853627984245161</v>
+        <v>0.15544202323866671</v>
       </c>
       <c r="L2">
-        <v>0.716448235665806</v>
+        <v>0.65685497488860567</v>
       </c>
       <c r="M2">
-        <v>0.04902189175698916</v>
+        <v>0.1081386481015139</v>
       </c>
       <c r="N2">
-        <v>0.7157755117604122</v>
+        <v>0.56261289233149214</v>
       </c>
       <c r="O2">
-        <v>0.03541174498437542</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>6.9276647103779176E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.6047619047619047</v>
+        <v>0.67142857142857149</v>
       </c>
       <c r="C3">
-        <v>0.08518354199999199</v>
+        <v>0.19948914348241351</v>
       </c>
       <c r="D3">
-        <v>0.5714285714285714</v>
+        <v>0.75714285714285723</v>
       </c>
       <c r="E3">
-        <v>0.08748177652797065</v>
+        <v>0.16530052340675991</v>
       </c>
       <c r="F3">
-        <v>0.6047619047619047</v>
+        <v>0.66190476190476188</v>
       </c>
       <c r="G3">
-        <v>0.08518354199999199</v>
+        <v>0.19806318421986119</v>
       </c>
       <c r="H3">
-        <v>0.6047619047619047</v>
+        <v>0.61428571428571432</v>
       </c>
       <c r="I3">
-        <v>0.08518354199999199</v>
+        <v>0.2706337569215776</v>
       </c>
       <c r="J3">
-        <v>0.5714285714285714</v>
+        <v>0.72857142857142854</v>
       </c>
       <c r="K3">
-        <v>0.08748177652797065</v>
+        <v>0.2113556287730681</v>
       </c>
       <c r="L3">
-        <v>0.5714285714285714</v>
+        <v>0.67619047619047623</v>
       </c>
       <c r="M3">
-        <v>0.08748177652797065</v>
+        <v>0.2113556287730681</v>
       </c>
       <c r="N3">
-        <v>0.5714285714285714</v>
+        <v>0.45714285714285707</v>
       </c>
       <c r="O3">
-        <v>0.08748177652797065</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>0.2371409447235949</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.6824525280256234</v>
+        <v>0.59471516815374048</v>
       </c>
       <c r="C4">
-        <v>0.03025055747154673</v>
+        <v>9.3540984584939091E-2</v>
       </c>
       <c r="D4">
-        <v>0.7060398078242965</v>
+        <v>0.57282086479066574</v>
       </c>
       <c r="E4">
-        <v>0.05051730001818518</v>
+        <v>8.9496414798411861E-2</v>
       </c>
       <c r="F4">
-        <v>0.7166781056966369</v>
+        <v>0.52576069549302218</v>
       </c>
       <c r="G4">
-        <v>0.06595126079253961</v>
+        <v>0.16711848084811601</v>
       </c>
       <c r="H4">
-        <v>0.6974376572866622</v>
+        <v>0.60542210020590259</v>
       </c>
       <c r="I4">
-        <v>0.03500100176534015</v>
+        <v>0.1155974285117565</v>
       </c>
       <c r="J4">
-        <v>0.6952871196522535</v>
+        <v>0.53438572409059715</v>
       </c>
       <c r="K4">
-        <v>0.03602789635377044</v>
+        <v>8.7824995449378884E-2</v>
       </c>
       <c r="L4">
-        <v>0.6995881949210707</v>
+        <v>0.52155113246396712</v>
       </c>
       <c r="M4">
-        <v>0.04145685007100892</v>
+        <v>9.0096707685225402E-2</v>
       </c>
       <c r="N4">
-        <v>0.6952642415923129</v>
+        <v>0.60077785403797757</v>
       </c>
       <c r="O4">
-        <v>0.01657909722605517</v>
+        <v>9.9312522461146857E-2</v>
       </c>
     </row>
   </sheetData>
@@ -618,11 +633,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,145 +681,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.6952212090509962</v>
+        <v>0.70660032029283903</v>
       </c>
       <c r="C2">
-        <v>0.08105318699970293</v>
+        <v>7.2438491613000977E-2</v>
       </c>
       <c r="D2">
-        <v>0.7215154535847741</v>
+        <v>0.70891590678824712</v>
       </c>
       <c r="E2">
-        <v>0.1214615059207974</v>
+        <v>5.8242152130019743E-2</v>
       </c>
       <c r="F2">
-        <v>0.6293688923750695</v>
+        <v>0.70218594415574509</v>
       </c>
       <c r="G2">
-        <v>0.03943202183913422</v>
+        <v>7.348025488701905E-2</v>
       </c>
       <c r="H2">
-        <v>0.6491556906450523</v>
+        <v>0.72117909163207727</v>
       </c>
       <c r="I2">
-        <v>0.1106884314259497</v>
+        <v>5.0417318226672322E-2</v>
       </c>
       <c r="J2">
-        <v>0.7065142552102058</v>
+        <v>0.73489830157640723</v>
       </c>
       <c r="K2">
-        <v>0.1554420232386667</v>
+        <v>7.6066870591646074E-2</v>
       </c>
       <c r="L2">
-        <v>0.6568549748886057</v>
+        <v>0.73940255580612479</v>
       </c>
       <c r="M2">
-        <v>0.1081386481015139</v>
+        <v>5.070249026532829E-2</v>
       </c>
       <c r="N2">
-        <v>0.5626128923314921</v>
+        <v>0.69019620659977554</v>
       </c>
       <c r="O2">
-        <v>0.06927664710377918</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>5.8292077203194757E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.6714285714285715</v>
+        <v>0.7</v>
       </c>
       <c r="C3">
-        <v>0.1994891434824135</v>
+        <v>0.17136242109949129</v>
       </c>
       <c r="D3">
-        <v>0.7571428571428572</v>
+        <v>0.61428571428571432</v>
       </c>
       <c r="E3">
-        <v>0.1653005234067599</v>
+        <v>0.20647127036836951</v>
       </c>
       <c r="F3">
-        <v>0.6619047619047619</v>
+        <v>0.72857142857142865</v>
       </c>
       <c r="G3">
-        <v>0.1980631842198612</v>
+        <v>0.1185704723617975</v>
       </c>
       <c r="H3">
-        <v>0.6142857142857143</v>
+        <v>0.7</v>
       </c>
       <c r="I3">
-        <v>0.2706337569215776</v>
+        <v>0.17136242109949129</v>
       </c>
       <c r="J3">
-        <v>0.7285714285714285</v>
+        <v>0.7</v>
       </c>
       <c r="K3">
-        <v>0.2113556287730681</v>
+        <v>0.13842325574998701</v>
       </c>
       <c r="L3">
-        <v>0.6761904761904762</v>
+        <v>0.7</v>
       </c>
       <c r="M3">
-        <v>0.2113556287730681</v>
+        <v>0.13842325574998701</v>
       </c>
       <c r="N3">
-        <v>0.4571428571428571</v>
+        <v>0.60952380952380947</v>
       </c>
       <c r="O3">
-        <v>0.2371409447235949</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>5.2164053095730113E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.5947151681537405</v>
+        <v>0.66744452070464422</v>
       </c>
       <c r="C4">
-        <v>0.09354098458493909</v>
+        <v>6.3598866923973832E-2</v>
       </c>
       <c r="D4">
-        <v>0.5728208647906657</v>
+        <v>0.6995424388011896</v>
       </c>
       <c r="E4">
-        <v>0.08949641479841186</v>
+        <v>4.887462600348768E-2</v>
       </c>
       <c r="F4">
-        <v>0.5257606954930222</v>
+        <v>0.52807137954701433</v>
       </c>
       <c r="G4">
-        <v>0.167118480848116</v>
+        <v>0.117223258902481</v>
       </c>
       <c r="H4">
-        <v>0.6054221002059026</v>
+        <v>0.64600777854037972</v>
       </c>
       <c r="I4">
-        <v>0.1155974285117565</v>
+        <v>6.9472479064461731E-2</v>
       </c>
       <c r="J4">
-        <v>0.5343857240905971</v>
+        <v>0.6673758865248226</v>
       </c>
       <c r="K4">
-        <v>0.08782499544937888</v>
+        <v>7.0936578302607342E-2</v>
       </c>
       <c r="L4">
-        <v>0.5215511324639671</v>
+        <v>0.66097002974147789</v>
       </c>
       <c r="M4">
-        <v>0.0900967076852254</v>
+        <v>5.7483054837407413E-2</v>
       </c>
       <c r="N4">
-        <v>0.6007778540379776</v>
+        <v>0.69103180050331725</v>
       </c>
       <c r="O4">
-        <v>0.09931252246114686</v>
+        <v>4.2140367939430802E-2</v>
       </c>
     </row>
   </sheetData>
@@ -813,11 +828,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,145 +876,145 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.706600320292839</v>
+        <v>0.71308189256027288</v>
       </c>
       <c r="C2">
-        <v>0.07243849161300098</v>
+        <v>6.4944544051854958E-2</v>
       </c>
       <c r="D2">
-        <v>0.7089159067882471</v>
+        <v>0.7150809992265037</v>
       </c>
       <c r="E2">
-        <v>0.05824215213001974</v>
+        <v>4.8658042666525507E-2</v>
       </c>
       <c r="F2">
-        <v>0.7021859441557451</v>
+        <v>0.71768092732402944</v>
       </c>
       <c r="G2">
-        <v>0.07348025488701905</v>
+        <v>5.3534823888659482E-2</v>
       </c>
       <c r="H2">
-        <v>0.7211790916320773</v>
+        <v>0.71516434073057267</v>
       </c>
       <c r="I2">
-        <v>0.05041731822667232</v>
+        <v>6.2499256471031939E-2</v>
       </c>
       <c r="J2">
-        <v>0.7348983015764072</v>
+        <v>0.71807911451013717</v>
       </c>
       <c r="K2">
-        <v>0.07606687059164607</v>
+        <v>4.853627984245161E-2</v>
       </c>
       <c r="L2">
-        <v>0.7394025558061248</v>
+        <v>0.71644823566580595</v>
       </c>
       <c r="M2">
-        <v>0.05070249026532829</v>
+        <v>4.9021891756989157E-2</v>
       </c>
       <c r="N2">
-        <v>0.6901962065997755</v>
+        <v>0.71577551176041221</v>
       </c>
       <c r="O2">
-        <v>0.05829207720319476</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>3.5411744984375423E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>0.7</v>
+        <v>0.60476190476190472</v>
       </c>
       <c r="C3">
-        <v>0.1713624210994913</v>
+        <v>8.5183541999991993E-2</v>
       </c>
       <c r="D3">
-        <v>0.6142857142857143</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E3">
-        <v>0.2064712703683695</v>
+        <v>8.7481776527970651E-2</v>
       </c>
       <c r="F3">
-        <v>0.7285714285714286</v>
+        <v>0.60476190476190472</v>
       </c>
       <c r="G3">
-        <v>0.1185704723617975</v>
+        <v>8.5183541999991993E-2</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>0.60476190476190472</v>
       </c>
       <c r="I3">
-        <v>0.1713624210994913</v>
+        <v>8.5183541999991993E-2</v>
       </c>
       <c r="J3">
-        <v>0.7</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K3">
-        <v>0.138423255749987</v>
+        <v>8.7481776527970651E-2</v>
       </c>
       <c r="L3">
-        <v>0.7</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M3">
-        <v>0.138423255749987</v>
+        <v>8.7481776527970651E-2</v>
       </c>
       <c r="N3">
-        <v>0.6095238095238095</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="O3">
-        <v>0.05216405309573011</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>8.7481776527970651E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.6674445207046442</v>
+        <v>0.6824525280256234</v>
       </c>
       <c r="C4">
-        <v>0.06359886692397383</v>
+        <v>3.025055747154673E-2</v>
       </c>
       <c r="D4">
-        <v>0.6995424388011896</v>
+        <v>0.70603980782429654</v>
       </c>
       <c r="E4">
-        <v>0.04887462600348768</v>
+        <v>5.0517300018185177E-2</v>
       </c>
       <c r="F4">
-        <v>0.5280713795470143</v>
+        <v>0.71667810569663692</v>
       </c>
       <c r="G4">
-        <v>0.117223258902481</v>
+        <v>6.5951260792539615E-2</v>
       </c>
       <c r="H4">
-        <v>0.6460077785403797</v>
+        <v>0.69743765728666218</v>
       </c>
       <c r="I4">
-        <v>0.06947247906446173</v>
+        <v>3.5001001765340149E-2</v>
       </c>
       <c r="J4">
-        <v>0.6673758865248226</v>
+        <v>0.69528711965225354</v>
       </c>
       <c r="K4">
-        <v>0.07093657830260734</v>
+        <v>3.602789635377044E-2</v>
       </c>
       <c r="L4">
-        <v>0.6609700297414779</v>
+        <v>0.69958819492107072</v>
       </c>
       <c r="M4">
-        <v>0.05748305483740741</v>
+        <v>4.1456850071008917E-2</v>
       </c>
       <c r="N4">
-        <v>0.6910318005033173</v>
+        <v>0.69526424159231293</v>
       </c>
       <c r="O4">
-        <v>0.0421403679394308</v>
+        <v>1.6579097226055169E-2</v>
       </c>
     </row>
   </sheetData>
